--- a/ke_hoach_VCL2026.xlsx
+++ b/ke_hoach_VCL2026.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -138,6 +138,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,9 +615,9 @@
           <t>30 phút</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Chưa</t>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>Xong</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -664,9 +667,9 @@
           <t>30 phút</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Chưa</t>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Xong</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -716,9 +719,9 @@
           <t>20 phút</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Chưa</t>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Xong</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -924,9 +927,9 @@
           <t>1 giờ</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Chưa</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Xong</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
